--- a/artfynd/A 11436-2026 artfynd.xlsx
+++ b/artfynd/A 11436-2026 artfynd.xlsx
@@ -1879,10 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132749707</v>
+        <v>132749718</v>
       </c>
       <c r="B14" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,21 +1890,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427988</v>
+        <v>427888</v>
       </c>
       <c r="R14" t="n">
-        <v>7024592</v>
+        <v>7024669</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,11 +1950,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1981,10 +1976,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132749718</v>
+        <v>132749707</v>
       </c>
       <c r="B15" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1992,21 +1987,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2016,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427888</v>
+        <v>427988</v>
       </c>
       <c r="R15" t="n">
-        <v>7024669</v>
+        <v>7024592</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,6 +2047,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2078,10 +2078,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132749694</v>
+        <v>132749716</v>
       </c>
       <c r="B16" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,21 +2089,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>428040</v>
+        <v>427934</v>
       </c>
       <c r="R16" t="n">
-        <v>7024574</v>
+        <v>7024483</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2149,11 +2149,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2180,7 +2175,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132749692</v>
+        <v>132749694</v>
       </c>
       <c r="B17" t="n">
         <v>57953</v>
@@ -2215,10 +2210,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>427964</v>
+        <v>428040</v>
       </c>
       <c r="R17" t="n">
-        <v>7024607</v>
+        <v>7024574</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2255,7 +2250,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska (årets) och äldre</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2282,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132749716</v>
+        <v>132749692</v>
       </c>
       <c r="B18" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2293,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2317,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>427934</v>
+        <v>427964</v>
       </c>
       <c r="R18" t="n">
-        <v>7024483</v>
+        <v>7024607</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2353,6 +2348,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska (årets) och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2790,7 +2790,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132749690</v>
+        <v>132749700</v>
       </c>
       <c r="B23" t="n">
         <v>57953</v>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>427891</v>
+        <v>427935</v>
       </c>
       <c r="R23" t="n">
-        <v>7024551</v>
+        <v>7024523</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2892,7 +2892,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132749700</v>
+        <v>132749690</v>
       </c>
       <c r="B24" t="n">
         <v>57953</v>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>427935</v>
+        <v>427891</v>
       </c>
       <c r="R24" t="n">
-        <v>7024523</v>
+        <v>7024551</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 11436-2026 artfynd.xlsx
+++ b/artfynd/A 11436-2026 artfynd.xlsx
@@ -1879,10 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132749718</v>
+        <v>132749707</v>
       </c>
       <c r="B14" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,21 +1890,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427888</v>
+        <v>427988</v>
       </c>
       <c r="R14" t="n">
-        <v>7024669</v>
+        <v>7024592</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,6 +1950,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1976,10 +1981,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132749707</v>
+        <v>132749718</v>
       </c>
       <c r="B15" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1987,21 +1992,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2011,10 +2016,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427988</v>
+        <v>427888</v>
       </c>
       <c r="R15" t="n">
-        <v>7024592</v>
+        <v>7024669</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2047,11 +2052,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 11436-2026 artfynd.xlsx
+++ b/artfynd/A 11436-2026 artfynd.xlsx
@@ -1680,7 +1680,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132749721</v>
+        <v>132749719</v>
       </c>
       <c r="B12" t="n">
         <v>79327</v>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427986</v>
+        <v>427934</v>
       </c>
       <c r="R12" t="n">
-        <v>7024587</v>
+        <v>7024652</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,6 +1751,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,7 +1782,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132749719</v>
+        <v>132749721</v>
       </c>
       <c r="B13" t="n">
         <v>79327</v>
@@ -1812,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427934</v>
+        <v>427986</v>
       </c>
       <c r="R13" t="n">
-        <v>7024652</v>
+        <v>7024587</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,11 +1853,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1879,10 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132749707</v>
+        <v>132749718</v>
       </c>
       <c r="B14" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,21 +1890,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427988</v>
+        <v>427888</v>
       </c>
       <c r="R14" t="n">
-        <v>7024592</v>
+        <v>7024669</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,11 +1950,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1981,10 +1976,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132749718</v>
+        <v>132749707</v>
       </c>
       <c r="B15" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1992,21 +1987,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2016,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427888</v>
+        <v>427988</v>
       </c>
       <c r="R15" t="n">
-        <v>7024669</v>
+        <v>7024592</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,6 +2047,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2078,10 +2078,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132749716</v>
+        <v>132749694</v>
       </c>
       <c r="B16" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,21 +2089,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>427934</v>
+        <v>428040</v>
       </c>
       <c r="R16" t="n">
-        <v>7024483</v>
+        <v>7024574</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2149,6 +2149,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2175,7 +2180,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132749694</v>
+        <v>132749692</v>
       </c>
       <c r="B17" t="n">
         <v>57953</v>
@@ -2210,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>428040</v>
+        <v>427964</v>
       </c>
       <c r="R17" t="n">
-        <v>7024574</v>
+        <v>7024607</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2250,7 +2255,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Ringhack färska (årets) och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2277,10 +2282,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132749692</v>
+        <v>132749716</v>
       </c>
       <c r="B18" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2293,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>427964</v>
+        <v>427934</v>
       </c>
       <c r="R18" t="n">
-        <v>7024607</v>
+        <v>7024483</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,11 +2353,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska (årets) och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 11436-2026 artfynd.xlsx
+++ b/artfynd/A 11436-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132749691</v>
       </c>
       <c r="B2" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>132749714</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>132749720</v>
       </c>
       <c r="B4" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>132749699</v>
       </c>
       <c r="B5" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>132749713</v>
       </c>
       <c r="B6" t="n">
-        <v>91905</v>
+        <v>91906</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>132749701</v>
       </c>
       <c r="B7" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>132749693</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>132749706</v>
       </c>
       <c r="B9" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>132749704</v>
       </c>
       <c r="B10" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>132749702</v>
       </c>
       <c r="B11" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132749719</v>
+        <v>132749721</v>
       </c>
       <c r="B12" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427934</v>
+        <v>427986</v>
       </c>
       <c r="R12" t="n">
-        <v>7024652</v>
+        <v>7024587</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,11 +1751,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,10 +1777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132749721</v>
+        <v>132749719</v>
       </c>
       <c r="B13" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1817,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427986</v>
+        <v>427934</v>
       </c>
       <c r="R13" t="n">
-        <v>7024587</v>
+        <v>7024652</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1853,6 +1848,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1879,10 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132749718</v>
+        <v>132749707</v>
       </c>
       <c r="B14" t="n">
-        <v>79327</v>
+        <v>57954</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,21 +1890,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427888</v>
+        <v>427988</v>
       </c>
       <c r="R14" t="n">
-        <v>7024669</v>
+        <v>7024592</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,6 +1950,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1976,10 +1981,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132749707</v>
+        <v>132749718</v>
       </c>
       <c r="B15" t="n">
-        <v>57953</v>
+        <v>79328</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1987,21 +1992,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2011,10 +2016,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427988</v>
+        <v>427888</v>
       </c>
       <c r="R15" t="n">
-        <v>7024592</v>
+        <v>7024669</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2047,11 +2052,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2078,10 +2078,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132749694</v>
+        <v>132749716</v>
       </c>
       <c r="B16" t="n">
-        <v>57953</v>
+        <v>79328</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,21 +2089,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>428040</v>
+        <v>427934</v>
       </c>
       <c r="R16" t="n">
-        <v>7024574</v>
+        <v>7024483</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2149,11 +2149,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2180,10 +2175,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132749692</v>
+        <v>132749694</v>
       </c>
       <c r="B17" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2215,10 +2210,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>427964</v>
+        <v>428040</v>
       </c>
       <c r="R17" t="n">
-        <v>7024607</v>
+        <v>7024574</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2255,7 +2250,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska (årets) och äldre</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2282,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132749716</v>
+        <v>132749692</v>
       </c>
       <c r="B18" t="n">
-        <v>79327</v>
+        <v>57954</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2293,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2317,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>427934</v>
+        <v>427964</v>
       </c>
       <c r="R18" t="n">
-        <v>7024483</v>
+        <v>7024607</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2353,6 +2348,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska (årets) och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2382,7 +2382,7 @@
         <v>132749696</v>
       </c>
       <c r="B19" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>132749695</v>
       </c>
       <c r="B20" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>132749705</v>
       </c>
       <c r="B21" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>132749717</v>
       </c>
       <c r="B22" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>132749700</v>
       </c>
       <c r="B23" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>132749690</v>
       </c>
       <c r="B24" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
